--- a/s100_ports/Altair_S100_Port_Assignments.xlsx
+++ b/s100_ports/Altair_S100_Port_Assignments.xlsx
@@ -12,13 +12,15 @@
     <sheet name="Third-Party Cards" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Port Map 00-FF" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Memory-Mapped" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Sources" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="RC2014 (RCBus)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sources" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MITS Altair'!$A$1:$L$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Third-Party Cards'!$A$1:$L$105</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Port Map 00-FF'!$A$1:$F$257</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Memory-Mapped'!$A$1:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'RC2014 (RCBus)'!$A$1:$I$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,6 +72,10 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00B42318"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <color rgb="00B42318"/>
       <sz val="10"/>
     </font>
@@ -184,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -291,7 +297,25 @@
     <xf numFmtId="0" fontId="5" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -659,7 +683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C18"/>
+  <dimension ref="B2:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -688,7 +712,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="66" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Sheets</t>
@@ -696,7 +720,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>MITS Altair - every MITS/Altair board with a documented port.  Third-Party Cards - the major S-100 makers.  Port Map 00-FF - a byte-by-byte index showing who claims each port and where they collide.  Memory-Mapped - controllers that live in memory space and use no ports at all.  Sources - what each row is based on.</t>
+          <t>MITS Altair - every MITS/Altair board with a documented port.  Third-Party Cards - the major S-100 makers.  Port Map 00-FF - a byte-by-byte index showing who claims each port and where they collide.  Memory-Mapped - controllers that live in memory space and use no ports at all.  RC2014 - a separate modern bus, see the note below.  Sources - what each row is based on.</t>
         </is>
       </c>
     </row>
@@ -760,13 +784,25 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="38" customHeight="1">
+    <row r="18" ht="62" customHeight="1">
       <c r="B18" s="8" t="inlineStr">
         <is>
+          <t>RC2014 is separate</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>The RC2014 sheet is a DIFFERENT BUS. RC2014 / RCBus is a modern homebrew Z80 backplane from 2014 onward. It shares the Z80 and the 8-bit port space with the machines above and nothing else - no board, no address convention and no manufacturer carries across. It is included because the same question, 'what is already using this port?', has the same shape. Do not read an address from that sheet onto an S-100 machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="38" customHeight="1">
+      <c r="B20" s="8" t="inlineStr">
+        <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>This covers the manufacturers whose cards you actually meet in Altair-era systems. Several hundred S-100 boards were made in total, and a long tail of them - mostly memory, prototyping and one-off cards - is not represented here.</t>
         </is>
@@ -15571,7 +15607,2452 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:I57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="68" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Origin</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Module / Card</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>Ports</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>Alternative / echo addresses</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>RC2014 Mini's Serial</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Spencer Owen</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>Serial</t>
+        </is>
+      </c>
+      <c r="F2" s="38" t="inlineStr">
+        <is>
+          <t>0x80-0x83</t>
+        </is>
+      </c>
+      <c r="G2" s="38" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H2" s="39" t="inlineStr">
+        <is>
+          <t>0x84-0xBF</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Serial I/O (68B50 UART)</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Spencer Owen</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Serial</t>
+        </is>
+      </c>
+      <c r="F3" s="38" t="inlineStr">
+        <is>
+          <t>0x80-0x83</t>
+        </is>
+      </c>
+      <c r="G3" s="38" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H3" s="39" t="inlineStr">
+        <is>
+          <t>0x84-0xBF</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Dual Serial (SIO/2 UART)</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Spencer Owen</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Serial</t>
+        </is>
+      </c>
+      <c r="F4" s="38" t="inlineStr">
+        <is>
+          <t>0x80-0x83</t>
+        </is>
+      </c>
+      <c r="G4" s="38" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H4" s="39" t="inlineStr">
+        <is>
+          <t>0x84-0x87</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Digital I/O v1</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Spencer Owen</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>Parallel</t>
+        </is>
+      </c>
+      <c r="F5" s="38" t="inlineStr">
+        <is>
+          <t>0x00-0x03</t>
+        </is>
+      </c>
+      <c r="G5" s="38" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H5" s="39" t="inlineStr">
+        <is>
+          <t>0x04-0x7F</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Digital I/O v2</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Spencer Owen</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>Parallel</t>
+        </is>
+      </c>
+      <c r="F6" s="38" t="inlineStr">
+        <is>
+          <t>0x00-0x03</t>
+        </is>
+      </c>
+      <c r="G6" s="38" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H6" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Digital Input</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Spencer Owen</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>Parallel</t>
+        </is>
+      </c>
+      <c r="F7" s="38" t="inlineStr">
+        <is>
+          <t>0x00-0x03</t>
+        </is>
+      </c>
+      <c r="G7" s="38" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H7" s="39" t="inlineStr">
+        <is>
+          <t>0x04-0x7F</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Digital Output</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Spencer Owen</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>Parallel</t>
+        </is>
+      </c>
+      <c r="F8" s="38" t="inlineStr">
+        <is>
+          <t>0x00-0x03</t>
+        </is>
+      </c>
+      <c r="G8" s="38" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H8" s="39" t="inlineStr">
+        <is>
+          <t>0x04-0x7F</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Joystick</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Spencer Owen</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>Parallel</t>
+        </is>
+      </c>
+      <c r="F9" s="38" t="inlineStr">
+        <is>
+          <t>0x00-0x03</t>
+        </is>
+      </c>
+      <c r="G9" s="38" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H9" s="39" t="inlineStr">
+        <is>
+          <t>0x04-0x7F</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Compact Flash</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Spencer Owen</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="F10" s="38" t="inlineStr">
+        <is>
+          <t>0x10-0x17</t>
+        </is>
+      </c>
+      <c r="G10" s="38" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H10" s="39" t="inlineStr">
+        <is>
+          <t>0x90-0x97</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>IDE (82C55 PIO)</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Ed Brindley &amp; Spencer</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="F11" s="38" t="inlineStr">
+        <is>
+          <t>0x20-0x23</t>
+        </is>
+      </c>
+      <c r="G11" s="38" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H11" s="39" t="inlineStr">
+        <is>
+          <t>0x10-0x13, 0x30-0x33, 0x40-0x43, 0x50-0x53, 0x60-0x63, 0x70-0x73, 0x80-0x83, 0x90-0x93, 0xA0-0xA3, 0xB0-0xB3, 0xC0-0xC3, 0xD0-0xD3, 0xE0-0xE3, 0xF0-0xF3</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Pageable ROM</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Spencer Owen</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>Memory / paging</t>
+        </is>
+      </c>
+      <c r="F12" s="38" t="inlineStr">
+        <is>
+          <t>0x30-0x3F</t>
+        </is>
+      </c>
+      <c r="G12" s="38" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H12" s="39" t="inlineStr">
+        <is>
+          <t>0xB0-0xBF</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Serial I/O (16550 UART)</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Ben Chong</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Serial</t>
+        </is>
+      </c>
+      <c r="F13" s="38" t="inlineStr">
+        <is>
+          <t>0x80-0x87</t>
+        </is>
+      </c>
+      <c r="G13" s="38" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H13" s="39" t="inlineStr">
+        <is>
+          <t>0x88-0xFF</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Digital I/O / LCD (8255)</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Thomas Riesen</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>Parallel</t>
+        </is>
+      </c>
+      <c r="F14" s="38" t="inlineStr">
+        <is>
+          <t>0x00-0x03</t>
+        </is>
+      </c>
+      <c r="G14" s="38" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H14" s="39" t="inlineStr">
+        <is>
+          <t>0x04-0xFF</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Sound Card (AY/YM)</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Ed Brindley</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="F15" s="38" t="inlineStr">
+        <is>
+          <t>0xD8-0xDB</t>
+        </is>
+      </c>
+      <c r="G15" s="38" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H15" s="39" t="inlineStr">
+        <is>
+          <t>0xD4-0xD7</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Sound Card (AY/YM)</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Ed Brindley</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="F16" s="38" t="inlineStr">
+        <is>
+          <t>0xD0-0xD3, 0xD8-0xDB</t>
+        </is>
+      </c>
+      <c r="G16" s="38" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H16" s="39" t="inlineStr">
+        <is>
+          <t>0xD4-0xD7</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Floppy Disk Controller</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Dr Scott M Baker</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>Floppy</t>
+        </is>
+      </c>
+      <c r="F17" s="38" t="inlineStr">
+        <is>
+          <t>0xE0-0xEB, 0xF0-0xF3, 0xF8-0xFF</t>
+        </is>
+      </c>
+      <c r="G17" s="38" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H17" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>VFD/LCD controller</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Dr Scott M Baker</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="F18" s="38" t="inlineStr">
+        <is>
+          <t>0xE0-0xE3</t>
+        </is>
+      </c>
+      <c r="G18" s="38" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H18" s="39" t="inlineStr">
+        <is>
+          <t>0xE4-0xEF</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Compact Flash</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Dr Scott M Baker</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="F19" s="38" t="inlineStr">
+        <is>
+          <t>0xE0-0xE7</t>
+        </is>
+      </c>
+      <c r="G19" s="38" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H19" s="39" t="inlineStr">
+        <is>
+          <t>0xE8-0xEF</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Z80 CTC</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Dr Scott M Baker</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>Timer</t>
+        </is>
+      </c>
+      <c r="F20" s="38" t="inlineStr">
+        <is>
+          <t>0xF0-0xF3</t>
+        </is>
+      </c>
+      <c r="G20" s="38" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H20" s="39" t="inlineStr">
+        <is>
+          <t>0xF4-0xFF</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Z80 SIO</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Dr Scott M Baker</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Serial</t>
+        </is>
+      </c>
+      <c r="F21" s="38" t="inlineStr">
+        <is>
+          <t>0xE0-0xE3</t>
+        </is>
+      </c>
+      <c r="G21" s="38" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H21" s="39" t="inlineStr">
+        <is>
+          <t>0xE4-0xE7</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Speech Synth. (SP0245A)</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Dr Scott M Baker</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="F22" s="38" t="inlineStr">
+        <is>
+          <t>0x70-0x73</t>
+        </is>
+      </c>
+      <c r="G22" s="38" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H22" s="39" t="inlineStr">
+        <is>
+          <t>0x74-0x7F</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Dual DAC (AD7524)</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Dr Scott M Baker</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="F23" s="38" t="inlineStr">
+        <is>
+          <t>0xE0-0xE3</t>
+        </is>
+      </c>
+      <c r="G23" s="38" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H23" s="39" t="inlineStr">
+        <is>
+          <t>0xE8-0xEB, 0xF0-0xF3, 0xF8-0xFB</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Front Panel (TIL311)</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Dr Scott M Baker</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="F24" s="38" t="inlineStr">
+        <is>
+          <t>0xE4-0xE7</t>
+        </is>
+      </c>
+      <c r="G24" s="38" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H24" s="39" t="inlineStr">
+        <is>
+          <t>0xEC-0xEF, 0xF4-0xF7, 0xFC-0xFF</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Front Panel (TIL311)</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Dr Scott M Baker</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="F25" s="38" t="inlineStr">
+        <is>
+          <t>0xE0-0xE3</t>
+        </is>
+      </c>
+      <c r="G25" s="38" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H25" s="39" t="inlineStr">
+        <is>
+          <t>0xE8-0xEB, 0xF0-0xF3, 0xF8-0xFB</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>RTClock (BEQ4845)</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Dr Scott M Baker</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>Clock</t>
+        </is>
+      </c>
+      <c r="F26" s="38" t="inlineStr">
+        <is>
+          <t>0xC0-0xCF</t>
+        </is>
+      </c>
+      <c r="G26" s="38" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H26" s="39" t="inlineStr">
+        <is>
+          <t>0xD0-0xDF</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>RTClock (BEQ4845)</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Dr Scott M Baker</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>Clock</t>
+        </is>
+      </c>
+      <c r="F27" s="38" t="inlineStr">
+        <is>
+          <t>0xC0-0xCF, 0xE0-0xE3</t>
+        </is>
+      </c>
+      <c r="G27" s="38" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H27" s="39" t="inlineStr">
+        <is>
+          <t>0xD0-0xDF, 0xE4-0xFF</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>LUT (Multiply) Module</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Phillip Stevens</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
+      <c r="F28" s="38" t="inlineStr">
+        <is>
+          <t>0x40-0x43</t>
+        </is>
+      </c>
+      <c r="G28" s="38" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H28" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Am9511 APU Module</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Phillip Stevens</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
+      <c r="F29" s="38" t="inlineStr">
+        <is>
+          <t>0x40-0x43</t>
+        </is>
+      </c>
+      <c r="G29" s="38" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H29" s="39" t="inlineStr">
+        <is>
+          <t>0x20-0x23, 0x60-0x63, 0x80-0x83, 0xA0-0xA3, 0xC0-0xC3, 0xE0-0xE3</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Digital I/O</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr"/>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>Parallel</t>
+        </is>
+      </c>
+      <c r="F30" s="34" t="inlineStr">
+        <is>
+          <t>0x00-0x03</t>
+        </is>
+      </c>
+      <c r="G30" s="34" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H30" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>Agrees with Cousins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="41" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B31" s="41" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="inlineStr">
+        <is>
+          <t>VFD (Scott Baker)</t>
+        </is>
+      </c>
+      <c r="D31" s="41" t="inlineStr"/>
+      <c r="E31" s="41" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="F31" s="31" t="inlineStr">
+        <is>
+          <t>0x00-0x01</t>
+        </is>
+      </c>
+      <c r="G31" s="31" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H31" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" s="43" t="inlineStr">
+        <is>
+          <t>Cousins puts this board at 0xE0-0xE3. The two lists disagree - verify against your own board.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>CF Adapter</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr"/>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="F32" s="34" t="inlineStr">
+        <is>
+          <t>0x10-0x17</t>
+        </is>
+      </c>
+      <c r="G32" s="34" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H32" s="40" t="inlineStr">
+        <is>
+          <t>0x90-0x97 (ghost)</t>
+        </is>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>Agrees with Cousins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="41" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B33" s="41" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="inlineStr">
+        <is>
+          <t>Speech Synthesizer (Scott Baker)</t>
+        </is>
+      </c>
+      <c r="D33" s="41" t="inlineStr"/>
+      <c r="E33" s="41" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="F33" s="31" t="inlineStr">
+        <is>
+          <t>0x20</t>
+        </is>
+      </c>
+      <c r="G33" s="31" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H33" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I33" s="43" t="inlineStr">
+        <is>
+          <t>Cousins puts this board at 0x70-0x73. The two lists disagree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>Pageable ROM</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr"/>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>Memory / paging</t>
+        </is>
+      </c>
+      <c r="F34" s="34" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="G34" s="34" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H34" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>Falls inside the 0x30-0x3F block Cousins gives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>SC108 banking / paging</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr"/>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>Memory / paging</t>
+        </is>
+      </c>
+      <c r="F35" s="34" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="G35" s="34" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H35" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
+        <is>
+          <t>Shares 0x38 with the pageable ROM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>Marco's Propeller Graphics Card</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr"/>
+      <c r="E36" s="25" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="F36" s="34" t="inlineStr">
+        <is>
+          <t>0x40-0x43</t>
+        </is>
+      </c>
+      <c r="G36" s="34" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H36" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>Collides with the LUT and Am9511 APU modules, which Cousins also puts at 0x40-0x43.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="41" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B37" s="41" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C37" s="32" t="inlineStr">
+        <is>
+          <t>Floppy Controller (Scott Baker)</t>
+        </is>
+      </c>
+      <c r="D37" s="41" t="inlineStr"/>
+      <c r="E37" s="41" t="inlineStr">
+        <is>
+          <t>Floppy</t>
+        </is>
+      </c>
+      <c r="F37" s="31" t="inlineStr">
+        <is>
+          <t>0x48-0x58</t>
+        </is>
+      </c>
+      <c r="G37" s="31" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H37" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" s="43" t="inlineStr">
+        <is>
+          <t>Cousins puts this board at 0xE0-0xEB, 0xF0-0xF3 and 0xF8-0xFF. A large disagreement - verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>SC103 Z80 PIO</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr"/>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>Parallel</t>
+        </is>
+      </c>
+      <c r="F38" s="34" t="inlineStr">
+        <is>
+          <t>0x68-0x6B</t>
+        </is>
+      </c>
+      <c r="G38" s="34" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H38" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" s="16" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>512K ROM/RAM paging registers</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr"/>
+      <c r="E39" s="23" t="inlineStr">
+        <is>
+          <t>Memory / paging</t>
+        </is>
+      </c>
+      <c r="F39" s="34" t="inlineStr">
+        <is>
+          <t>0x70-0x7F</t>
+        </is>
+      </c>
+      <c r="G39" s="34" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H39" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>The forum thread corrected an earlier 0x70/0x74 reading to 0x78-0x7C; Cox records the wider 0x70-0x7F decode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>ACIA (partial decode)</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr"/>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>Serial</t>
+        </is>
+      </c>
+      <c r="F40" s="34" t="inlineStr">
+        <is>
+          <t>0x80-0xBF</t>
+        </is>
+      </c>
+      <c r="G40" s="34" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H40" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>Partial decode - the 68B50 board answers across the whole range. Consistent with Cousins' 0x80-0x83 primary plus alternates up to 0xBF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>SIO</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr"/>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>Serial</t>
+        </is>
+      </c>
+      <c r="F41" s="34" t="inlineStr">
+        <is>
+          <t>0x80-0x83</t>
+        </is>
+      </c>
+      <c r="G41" s="34" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H41" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>Agrees with Cousins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>SC104 SIO</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr"/>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>Serial</t>
+        </is>
+      </c>
+      <c r="F42" s="34" t="inlineStr">
+        <is>
+          <t>0x80-0x83</t>
+        </is>
+      </c>
+      <c r="G42" s="34" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H42" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" s="16" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>SC104 SIO, second card</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr"/>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>Serial</t>
+        </is>
+      </c>
+      <c r="F43" s="34" t="inlineStr">
+        <is>
+          <t>0x84-0x87</t>
+        </is>
+      </c>
+      <c r="G43" s="34" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H43" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" s="16" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>SIO (Scott Baker)</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr"/>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>Serial</t>
+        </is>
+      </c>
+      <c r="F44" s="34" t="inlineStr">
+        <is>
+          <t>0x80-0x83</t>
+        </is>
+      </c>
+      <c r="G44" s="34" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H44" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
+        <is>
+          <t>Cox notes this board may order its ports differently from the standard RC2014 SIO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>SC102 CTC, first card</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr"/>
+      <c r="E45" s="23" t="inlineStr">
+        <is>
+          <t>Timer</t>
+        </is>
+      </c>
+      <c r="F45" s="34" t="inlineStr">
+        <is>
+          <t>0x88-0x8B</t>
+        </is>
+      </c>
+      <c r="G45" s="34" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H45" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" s="16" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>SC102 CTC, second card</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr"/>
+      <c r="E46" s="23" t="inlineStr">
+        <is>
+          <t>Timer</t>
+        </is>
+      </c>
+      <c r="F46" s="34" t="inlineStr">
+        <is>
+          <t>0x8C-0x8F</t>
+        </is>
+      </c>
+      <c r="G46" s="34" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H46" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" s="16" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="41" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B47" s="41" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C47" s="32" t="inlineStr">
+        <is>
+          <t>CTC (Scott Baker)</t>
+        </is>
+      </c>
+      <c r="D47" s="41" t="inlineStr"/>
+      <c r="E47" s="41" t="inlineStr">
+        <is>
+          <t>Timer</t>
+        </is>
+      </c>
+      <c r="F47" s="31" t="inlineStr">
+        <is>
+          <t>0x90-0x93</t>
+        </is>
+      </c>
+      <c r="G47" s="31" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H47" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" s="43" t="inlineStr">
+        <is>
+          <t>Cousins puts this board at 0xF0-0xF3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>Z280RC boot mode switch</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr"/>
+      <c r="E48" s="23" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="F48" s="34" t="inlineStr">
+        <is>
+          <t>0xA0</t>
+        </is>
+      </c>
+      <c r="G48" s="34" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H48" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" s="16" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>Z280RC RTC</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr"/>
+      <c r="E49" s="23" t="inlineStr">
+        <is>
+          <t>Clock</t>
+        </is>
+      </c>
+      <c r="F49" s="34" t="inlineStr">
+        <is>
+          <t>0xA2</t>
+        </is>
+      </c>
+      <c r="G49" s="34" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H49" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="16" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>Real Time Clock (Scott Baker)</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr"/>
+      <c r="E50" s="23" t="inlineStr">
+        <is>
+          <t>Clock</t>
+        </is>
+      </c>
+      <c r="F50" s="34" t="inlineStr">
+        <is>
+          <t>0xC0</t>
+        </is>
+      </c>
+      <c r="G50" s="34" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H50" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>Falls inside the 0xC0-0xCF block Cousins gives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>16550A (Ancient Computing)</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr"/>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>Serial</t>
+        </is>
+      </c>
+      <c r="F51" s="34" t="inlineStr">
+        <is>
+          <t>0xC0</t>
+        </is>
+      </c>
+      <c r="G51" s="34" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H51" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>Shares 0xC0 with two clock boards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>DS1302 RTC (Ed Brindley)</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr"/>
+      <c r="E52" s="23" t="inlineStr">
+        <is>
+          <t>Clock</t>
+        </is>
+      </c>
+      <c r="F52" s="34" t="inlineStr">
+        <is>
+          <t>0xC0</t>
+        </is>
+      </c>
+      <c r="G52" s="34" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H52" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>Shares 0xC0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>Z280RC IDE</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr"/>
+      <c r="E53" s="23" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="F53" s="34" t="inlineStr">
+        <is>
+          <t>0xC0-0xCF</t>
+        </is>
+      </c>
+      <c r="G53" s="34" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H53" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" s="16" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>YM-AY sound (Ed Brindley)</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="inlineStr"/>
+      <c r="E54" s="23" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="F54" s="34" t="inlineStr">
+        <is>
+          <t>0xD0-0xD3</t>
+        </is>
+      </c>
+      <c r="G54" s="34" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H54" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>Agrees with Cousins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>CF Adapter (Scott Baker)</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr"/>
+      <c r="E55" s="23" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="F55" s="34" t="inlineStr">
+        <is>
+          <t>0xE0-0xE7</t>
+        </is>
+      </c>
+      <c r="G55" s="34" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H55" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>Agrees with Cousins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>PPIDE (Ed Brindley)</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr"/>
+      <c r="E56" s="23" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="F56" s="34" t="inlineStr">
+        <is>
+          <t>0xE0-0xE7</t>
+        </is>
+      </c>
+      <c r="G56" s="34" t="inlineStr">
+        <is>
+          <t>R/W</t>
+        </is>
+      </c>
+      <c r="H56" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="16" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>Cox</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>Third-party</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr">
+        <is>
+          <t>DAC (Scott Baker)</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="inlineStr"/>
+      <c r="E57" s="23" t="inlineStr">
+        <is>
+          <t>Sound</t>
+        </is>
+      </c>
+      <c r="F57" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" s="34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" s="40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>Cox found no documented default. Cousins gives 0xE0-0xE3 for writes.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I57"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -15607,7 +18088,7 @@
           <t>Board occupies 16 consecutive addresses; jumper groups at 000/020/040/060/100/120... octal; per-PIA register layout; worked example at 020-037 octal</t>
         </is>
       </c>
-      <c r="C2" s="38" t="inlineStr">
+      <c r="C2" s="44" t="inlineStr">
         <is>
           <t>http://dunfield.classiccmp.org/s100c/mits/88_4pio.pdf</t>
         </is>
@@ -15624,7 +18105,7 @@
           <t>'The 88-VI (RTC) uses I/O address 254 (decimal) or 376 (octal)'</t>
         </is>
       </c>
-      <c r="C3" s="38" t="inlineStr">
+      <c r="C3" s="44" t="inlineStr">
         <is>
           <t>http://dunfield.classiccmp.org/s100c/mits/88_virtc.pdf</t>
         </is>
@@ -15641,7 +18122,7 @@
           <t>Two device addresses, jumper-selectable to any even octal address 000-376; A0 selects control vs data</t>
         </is>
       </c>
-      <c r="C4" s="38" t="inlineStr">
+      <c r="C4" s="44" t="inlineStr">
         <is>
           <t>http://dunfield.classiccmp.org/s100c/mits/88sio_2.pdf</t>
         </is>
@@ -15658,7 +18139,7 @@
           <t>Cassette interface addressing and octal selection charts</t>
         </is>
       </c>
-      <c r="C5" s="38" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>http://dunfield.classiccmp.org/s100c/mits/88_acr.pdf</t>
         </is>
@@ -15675,7 +18156,7 @@
           <t>88-2SIO at 10-13 hex as the MITS standard; 88-DISK at 8/9/0A; North Star and Micropolis memory windows; CompuPro and Cromemco board descriptions</t>
         </is>
       </c>
-      <c r="C6" s="38" t="inlineStr">
+      <c r="C6" s="44" t="inlineStr">
         <is>
           <t>http://bitsavers.trailing-edge.com/simh.trailing-edge.com_201206/pdf/altairz80_doc.pdf</t>
         </is>
@@ -15692,7 +18173,7 @@
           <t>Register-level maps for Tarbell, Cromemco 4/16/64FDC, CompuPro Disk1A/2/3/Selector/M-Drive/System Support 1, Interfacer 3, Morrow, iCOM, Jade, PMMI, Hayes, Sol-20, TU-ART, Dazzler</t>
         </is>
       </c>
-      <c r="C7" s="38" t="inlineStr">
+      <c r="C7" s="44" t="inlineStr">
         <is>
           <t>https://github.com/simh/simh/tree/master/AltairZ80</t>
         </is>
@@ -15709,7 +18190,7 @@
           <t>Independent confirmation of the MITS port map (SIO 0/1, printer 2/3, ACR 6/7, DCDD 8/9/0A, 2SIO 10-13, VI 0xFE, sense switches 0xFF), 88-HDSK via a 4PIO at 0xA0-0xA7, Tarbell F8-FD, Cromemco 30-34</t>
         </is>
       </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C8" s="44" t="inlineStr">
         <is>
           <t>https://github.com/dhansel/Altair8800</t>
         </is>
@@ -15726,7 +18207,7 @@
           <t>88-SIO at 0/1, 88-ACR at 6/7, 88-2SIO at 10/11 and 12/13; printer control port 02h</t>
         </is>
       </c>
-      <c r="C9" s="38" t="inlineStr">
+      <c r="C9" s="44" t="inlineStr">
         <is>
           <t>https://retrocmp.de/hardware/altair-8800/altair-8800-sim-manual.pdf</t>
         </is>
@@ -15743,7 +18224,7 @@
           <t>TU-ART switch settings and the multi-user port map: #1 A=20h B=50h, #2 A=60h B=70h, #3 A=80h</t>
         </is>
       </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C10" s="44" t="inlineStr">
         <is>
           <t>https://archive.org/details/023-4022-cromemco-cromix-manuals</t>
         </is>
@@ -15760,7 +18241,7 @@
           <t>Eight-port block on any multiple of 8; CompuPro default 10-17h; relative port 0-7 function table</t>
         </is>
       </c>
-      <c r="C11" s="38" t="inlineStr">
+      <c r="C11" s="44" t="inlineStr">
         <is>
           <t>https://archive.org/details/bitsavers_compupro18calManualMay83_3167199</t>
         </is>
@@ -15777,7 +18258,7 @@
           <t>SIO-2 default block 00-0F; IMSAI software uses 02/03 (TTY) and 04/05 (CRT); second board at 20-2F</t>
         </is>
       </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="C12" s="44" t="inlineStr">
         <is>
           <t>http://www.bitsavers.org/pdf/imsai/IMSAI_SIO2-2_B_Manual.pdf</t>
         </is>
@@ -15786,32 +18267,83 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>s100computers.com</t>
+          <t>Steve Cousins, RC2014 module spreadsheet</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>Board histories and addressing notes for MITS, Tarbell, Cromemco, CompuPro and Processor Technology cards</t>
-        </is>
-      </c>
-      <c r="C13" s="38" t="inlineStr">
-        <is>
-          <t>http://www.s100computers.com/</t>
+          <t>RC2014 module addresses - primary and alternative - for 25 official and third-party modules. Addresses are encoded as cell fill colours in the sheet</t>
+        </is>
+      </c>
+      <c r="C13" s="44" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1ZJ_Ju3Cyyz2whgunSGr12wxhsTDOqJJQ6BO4E0xVRKU/edit</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
+          <t>Alan Cox, RC2014 'Ports' file</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>An independent compilation of known default RC2014 port assignments, including boards absent from the Cousins sheet</t>
+        </is>
+      </c>
+      <c r="C14" s="44" t="inlineStr">
+        <is>
+          <t>https://github.com/EtchedPixels/RC2014/blob/master/Ports</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>rc2014-z80 group, 'Port numbers' thread</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Where both compilations are discussed and reconciled; source of the 512K paging correction</t>
+        </is>
+      </c>
+      <c r="C15" s="44" t="inlineStr">
+        <is>
+          <t>https://groups.google.com/g/rc2014-z80/c/8Kahl19nSYw</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>s100computers.com</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Board histories and addressing notes for MITS, Tarbell, Cromemco, CompuPro and Processor Technology cards</t>
+        </is>
+      </c>
+      <c r="C16" s="44" t="inlineStr">
+        <is>
+          <t>http://www.s100computers.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
           <t>deramp.com archive</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>North Star Horizon restoration notes (MDS controller occupies E800-EFFF); MITS and IMSAI documentation mirror</t>
         </is>
       </c>
-      <c r="C14" s="38" t="inlineStr">
+      <c r="C17" s="44" t="inlineStr">
         <is>
           <t>https://deramp.com/</t>
         </is>
@@ -15832,6 +18364,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
